--- a/docs/migration-orders/davin-operational-manual/antigravity/migration-process-handbook-antigravity-v8.xlsx
+++ b/docs/migration-orders/davin-operational-manual/antigravity/migration-process-handbook-antigravity-v8.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SaaS Project\trading-alerts-saas-public\docs\migration-orders\davin-operational-manual\antigravity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A76ADE13-0662-42CC-9FA9-48963FA1B866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82A82CD8-B323-4DB4-B19A-005D946CA127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5667,40 +5667,39 @@
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="24" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -5708,18 +5707,19 @@
     <xf numFmtId="0" fontId="20" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8928,31 +8928,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="103" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="102"/>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
+      <c r="B1" s="104"/>
+      <c r="C1" s="104"/>
+      <c r="D1" s="104"/>
+      <c r="E1" s="104"/>
     </row>
     <row r="2" spans="1:5" ht="40" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="105" t="s">
+      <c r="A2" s="112" t="s">
         <v>89</v>
       </c>
-      <c r="B2" s="102"/>
-      <c r="C2" s="102"/>
-      <c r="D2" s="102"/>
-      <c r="E2" s="102"/>
+      <c r="B2" s="104"/>
+      <c r="C2" s="104"/>
+      <c r="D2" s="104"/>
+      <c r="E2" s="104"/>
     </row>
     <row r="4" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="101" t="s">
+      <c r="A4" s="111" t="s">
         <v>90</v>
       </c>
-      <c r="B4" s="102"/>
-      <c r="C4" s="102"/>
-      <c r="D4" s="102"/>
-      <c r="E4" s="102"/>
+      <c r="B4" s="104"/>
+      <c r="C4" s="104"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
     </row>
     <row r="5" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="69" t="s">
@@ -9009,10 +9009,10 @@
       <c r="A9" s="110" t="s">
         <v>106</v>
       </c>
-      <c r="B9" s="102"/>
-      <c r="C9" s="102"/>
-      <c r="D9" s="102"/>
-      <c r="E9" s="102"/>
+      <c r="B9" s="104"/>
+      <c r="C9" s="104"/>
+      <c r="D9" s="104"/>
+      <c r="E9" s="104"/>
     </row>
     <row r="10" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="69" t="s">
@@ -9249,11 +9249,11 @@
       </c>
     </row>
     <row r="24" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="102"/>
-      <c r="B24" s="102"/>
-      <c r="C24" s="102"/>
-      <c r="D24" s="102"/>
-      <c r="E24" s="102"/>
+      <c r="A24" s="104"/>
+      <c r="B24" s="104"/>
+      <c r="C24" s="104"/>
+      <c r="D24" s="104"/>
+      <c r="E24" s="104"/>
     </row>
     <row r="25" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="78" t="s">
@@ -9264,51 +9264,51 @@
       <c r="A26" s="69" t="s">
         <v>162</v>
       </c>
-      <c r="B26" s="109" t="s">
+      <c r="B26" s="108" t="s">
         <v>163</v>
       </c>
-      <c r="C26" s="104"/>
-      <c r="D26" s="109"/>
-      <c r="E26" s="104"/>
+      <c r="C26" s="107"/>
+      <c r="D26" s="108"/>
+      <c r="E26" s="107"/>
     </row>
     <row r="27" spans="1:5" ht="64" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="74" t="s">
         <v>164</v>
       </c>
-      <c r="B27" s="103" t="s">
+      <c r="B27" s="109" t="s">
         <v>165</v>
       </c>
-      <c r="C27" s="104"/>
-      <c r="D27" s="103" t="s">
+      <c r="C27" s="107"/>
+      <c r="D27" s="109" t="s">
         <v>166</v>
       </c>
-      <c r="E27" s="104"/>
+      <c r="E27" s="107"/>
     </row>
     <row r="28" spans="1:5" ht="64" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="74" t="s">
         <v>167</v>
       </c>
-      <c r="B28" s="103" t="s">
+      <c r="B28" s="109" t="s">
         <v>168</v>
       </c>
-      <c r="C28" s="104"/>
-      <c r="D28" s="103" t="s">
+      <c r="C28" s="107"/>
+      <c r="D28" s="109" t="s">
         <v>169</v>
       </c>
-      <c r="E28" s="104"/>
+      <c r="E28" s="107"/>
     </row>
     <row r="29" spans="1:5" ht="64" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="74" t="s">
         <v>170</v>
       </c>
-      <c r="B29" s="103" t="s">
+      <c r="B29" s="109" t="s">
         <v>171</v>
       </c>
-      <c r="C29" s="104"/>
-      <c r="D29" s="103" t="s">
+      <c r="C29" s="107"/>
+      <c r="D29" s="109" t="s">
         <v>172</v>
       </c>
-      <c r="E29" s="104"/>
+      <c r="E29" s="107"/>
     </row>
     <row r="30" spans="1:5" ht="43.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="74" t="s">
@@ -9324,11 +9324,11 @@
       <c r="E30" s="79"/>
     </row>
     <row r="31" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="102"/>
-      <c r="B31" s="102"/>
-      <c r="C31" s="102"/>
-      <c r="D31" s="102"/>
-      <c r="E31" s="102"/>
+      <c r="A31" s="104"/>
+      <c r="B31" s="104"/>
+      <c r="C31" s="104"/>
+      <c r="D31" s="104"/>
+      <c r="E31" s="104"/>
     </row>
     <row r="32" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="81" t="s">
@@ -9396,13 +9396,13 @@
       <c r="E36" s="71"/>
     </row>
     <row r="37" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="107" t="s">
+      <c r="A37" s="105" t="s">
         <v>192</v>
       </c>
-      <c r="B37" s="108"/>
-      <c r="C37" s="108"/>
-      <c r="D37" s="108"/>
-      <c r="E37" s="104"/>
+      <c r="B37" s="106"/>
+      <c r="C37" s="106"/>
+      <c r="D37" s="106"/>
+      <c r="E37" s="107"/>
     </row>
     <row r="38" spans="1:5" ht="230.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="80" t="s">
@@ -9444,76 +9444,76 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="118" t="s">
         <v>194</v>
       </c>
-      <c r="B1" s="102"/>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
+      <c r="B1" s="104"/>
+      <c r="C1" s="104"/>
+      <c r="D1" s="104"/>
+      <c r="E1" s="104"/>
     </row>
     <row r="2" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="113" t="s">
         <v>195</v>
       </c>
-      <c r="B2" s="102"/>
-      <c r="C2" s="102"/>
-      <c r="D2" s="102"/>
-      <c r="E2" s="102"/>
+      <c r="B2" s="104"/>
+      <c r="C2" s="104"/>
+      <c r="D2" s="104"/>
+      <c r="E2" s="104"/>
     </row>
     <row r="4" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="115" t="s">
+      <c r="A4" s="119" t="s">
         <v>196</v>
       </c>
-      <c r="B4" s="102"/>
-      <c r="C4" s="102"/>
-      <c r="D4" s="102"/>
-      <c r="E4" s="102"/>
+      <c r="B4" s="104"/>
+      <c r="C4" s="104"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
     </row>
     <row r="5" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="113" t="s">
         <v>197</v>
       </c>
-      <c r="B5" s="102"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="102"/>
+      <c r="B5" s="104"/>
+      <c r="C5" s="104"/>
+      <c r="D5" s="104"/>
+      <c r="E5" s="104"/>
     </row>
     <row r="6" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="113" t="s">
         <v>198</v>
       </c>
-      <c r="B6" s="102"/>
-      <c r="C6" s="102"/>
-      <c r="D6" s="102"/>
-      <c r="E6" s="102"/>
+      <c r="B6" s="104"/>
+      <c r="C6" s="104"/>
+      <c r="D6" s="104"/>
+      <c r="E6" s="104"/>
     </row>
     <row r="7" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="113" t="s">
         <v>199</v>
       </c>
-      <c r="B7" s="102"/>
-      <c r="C7" s="102"/>
-      <c r="D7" s="102"/>
-      <c r="E7" s="102"/>
+      <c r="B7" s="104"/>
+      <c r="C7" s="104"/>
+      <c r="D7" s="104"/>
+      <c r="E7" s="104"/>
     </row>
     <row r="8" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="113" t="s">
         <v>200</v>
       </c>
-      <c r="B8" s="102"/>
-      <c r="C8" s="102"/>
-      <c r="D8" s="102"/>
-      <c r="E8" s="102"/>
+      <c r="B8" s="104"/>
+      <c r="C8" s="104"/>
+      <c r="D8" s="104"/>
+      <c r="E8" s="104"/>
     </row>
     <row r="10" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="116" t="s">
+      <c r="A10" s="115" t="s">
         <v>201</v>
       </c>
-      <c r="B10" s="102"/>
-      <c r="C10" s="102"/>
-      <c r="D10" s="102"/>
-      <c r="E10" s="102"/>
+      <c r="B10" s="104"/>
+      <c r="C10" s="104"/>
+      <c r="D10" s="104"/>
+      <c r="E10" s="104"/>
     </row>
     <row r="11" spans="1:5" ht="34" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="62" t="s">
@@ -9704,10 +9704,10 @@
     </row>
     <row r="22" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="114"/>
-      <c r="B22" s="108"/>
-      <c r="C22" s="108"/>
-      <c r="D22" s="108"/>
-      <c r="E22" s="104"/>
+      <c r="B22" s="106"/>
+      <c r="C22" s="106"/>
+      <c r="D22" s="106"/>
+      <c r="E22" s="107"/>
     </row>
     <row r="23" spans="1:5" ht="100.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="83" t="s">
@@ -9715,11 +9715,11 @@
       </c>
     </row>
     <row r="24" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="102"/>
-      <c r="B24" s="102"/>
-      <c r="C24" s="102"/>
-      <c r="D24" s="102"/>
-      <c r="E24" s="102"/>
+      <c r="A24" s="104"/>
+      <c r="B24" s="104"/>
+      <c r="C24" s="104"/>
+      <c r="D24" s="104"/>
+      <c r="E24" s="104"/>
     </row>
     <row r="25" spans="1:5" ht="34" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="60" t="s">
@@ -9761,22 +9761,22 @@
       </c>
     </row>
     <row r="28" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="117" t="s">
+      <c r="A28" s="116" t="s">
         <v>230</v>
       </c>
-      <c r="B28" s="108"/>
-      <c r="C28" s="108"/>
-      <c r="D28" s="108"/>
-      <c r="E28" s="104"/>
+      <c r="B28" s="106"/>
+      <c r="C28" s="106"/>
+      <c r="D28" s="106"/>
+      <c r="E28" s="107"/>
     </row>
     <row r="29" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="113" t="s">
         <v>231</v>
       </c>
-      <c r="B29" s="102"/>
-      <c r="C29" s="102"/>
-      <c r="D29" s="102"/>
-      <c r="E29" s="102"/>
+      <c r="B29" s="104"/>
+      <c r="C29" s="104"/>
+      <c r="D29" s="104"/>
+      <c r="E29" s="104"/>
     </row>
     <row r="30" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="83" t="s">
@@ -9784,11 +9784,11 @@
       </c>
     </row>
     <row r="31" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="102"/>
-      <c r="B31" s="102"/>
-      <c r="C31" s="102"/>
-      <c r="D31" s="102"/>
-      <c r="E31" s="102"/>
+      <c r="A31" s="104"/>
+      <c r="B31" s="104"/>
+      <c r="C31" s="104"/>
+      <c r="D31" s="104"/>
+      <c r="E31" s="104"/>
     </row>
     <row r="32" spans="1:5" ht="34" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="84" t="s">
@@ -9881,11 +9881,11 @@
       </c>
     </row>
     <row r="38" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="102"/>
-      <c r="B38" s="102"/>
-      <c r="C38" s="102"/>
-      <c r="D38" s="102"/>
-      <c r="E38" s="102"/>
+      <c r="A38" s="104"/>
+      <c r="B38" s="104"/>
+      <c r="C38" s="104"/>
+      <c r="D38" s="104"/>
+      <c r="E38" s="104"/>
     </row>
     <row r="39" spans="1:5" ht="34" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="85" t="s">
@@ -9896,67 +9896,67 @@
       <c r="A40" s="62" t="s">
         <v>252</v>
       </c>
-      <c r="B40" s="111" t="s">
+      <c r="B40" s="117" t="s">
         <v>253</v>
       </c>
-      <c r="C40" s="108"/>
-      <c r="D40" s="108"/>
-      <c r="E40" s="104"/>
+      <c r="C40" s="106"/>
+      <c r="D40" s="106"/>
+      <c r="E40" s="107"/>
     </row>
     <row r="41" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="63" t="s">
         <v>254</v>
       </c>
-      <c r="B41" s="103" t="s">
+      <c r="B41" s="109" t="s">
         <v>255</v>
       </c>
-      <c r="C41" s="108"/>
-      <c r="D41" s="108"/>
-      <c r="E41" s="104"/>
+      <c r="C41" s="106"/>
+      <c r="D41" s="106"/>
+      <c r="E41" s="107"/>
     </row>
     <row r="42" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="63" t="s">
         <v>256</v>
       </c>
-      <c r="B42" s="103" t="s">
+      <c r="B42" s="109" t="s">
         <v>257</v>
       </c>
-      <c r="C42" s="108"/>
-      <c r="D42" s="108"/>
-      <c r="E42" s="104"/>
+      <c r="C42" s="106"/>
+      <c r="D42" s="106"/>
+      <c r="E42" s="107"/>
     </row>
     <row r="43" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="63" t="s">
         <v>258</v>
       </c>
-      <c r="B43" s="103" t="s">
+      <c r="B43" s="109" t="s">
         <v>259</v>
       </c>
-      <c r="C43" s="108"/>
-      <c r="D43" s="108"/>
-      <c r="E43" s="104"/>
+      <c r="C43" s="106"/>
+      <c r="D43" s="106"/>
+      <c r="E43" s="107"/>
     </row>
     <row r="44" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="63" t="s">
         <v>260</v>
       </c>
-      <c r="B44" s="103" t="s">
+      <c r="B44" s="109" t="s">
         <v>261</v>
       </c>
-      <c r="C44" s="108"/>
-      <c r="D44" s="108"/>
-      <c r="E44" s="104"/>
+      <c r="C44" s="106"/>
+      <c r="D44" s="106"/>
+      <c r="E44" s="107"/>
     </row>
     <row r="45" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="63" t="s">
         <v>262</v>
       </c>
-      <c r="B45" s="103" t="s">
+      <c r="B45" s="109" t="s">
         <v>263</v>
       </c>
-      <c r="C45" s="108"/>
-      <c r="D45" s="108"/>
-      <c r="E45" s="104"/>
+      <c r="C45" s="106"/>
+      <c r="D45" s="106"/>
+      <c r="E45" s="107"/>
     </row>
     <row r="46" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="63" t="s">
@@ -9970,11 +9970,11 @@
       <c r="E46" s="79"/>
     </row>
     <row r="47" spans="1:5" ht="40" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="102"/>
-      <c r="B47" s="102"/>
-      <c r="C47" s="102"/>
-      <c r="D47" s="102"/>
-      <c r="E47" s="102"/>
+      <c r="A47" s="104"/>
+      <c r="B47" s="104"/>
+      <c r="C47" s="104"/>
+      <c r="D47" s="104"/>
+      <c r="E47" s="104"/>
     </row>
     <row r="48" spans="1:5" ht="86.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="84" t="s">
@@ -9983,6 +9983,14 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="A4:E4"/>
     <mergeCell ref="A47:E47"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A8:E8"/>
@@ -9996,14 +10004,6 @@
     <mergeCell ref="A31:E31"/>
     <mergeCell ref="B40:E40"/>
     <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="B43:E43"/>
-    <mergeCell ref="A4:E4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10024,20 +10024,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="26.05" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="120" t="s">
         <v>267</v>
       </c>
-      <c r="B1" s="102"/>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
+      <c r="B1" s="104"/>
+      <c r="C1" s="104"/>
+      <c r="D1" s="104"/>
     </row>
     <row r="2" spans="1:4" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="113" t="s">
         <v>268</v>
       </c>
-      <c r="B2" s="102"/>
-      <c r="C2" s="102"/>
-      <c r="D2" s="102"/>
+      <c r="B2" s="104"/>
+      <c r="C2" s="104"/>
+      <c r="D2" s="104"/>
     </row>
     <row r="4" spans="1:4" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="52" t="s">
@@ -10096,44 +10096,44 @@
       </c>
     </row>
     <row r="8" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="119" t="s">
+      <c r="A8" s="121" t="s">
         <v>285</v>
       </c>
-      <c r="B8" s="102"/>
-      <c r="C8" s="102"/>
-      <c r="D8" s="102"/>
+      <c r="B8" s="104"/>
+      <c r="C8" s="104"/>
+      <c r="D8" s="104"/>
     </row>
     <row r="9" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="113" t="s">
         <v>286</v>
       </c>
-      <c r="B9" s="102"/>
-      <c r="C9" s="102"/>
-      <c r="D9" s="102"/>
+      <c r="B9" s="104"/>
+      <c r="C9" s="104"/>
+      <c r="D9" s="104"/>
     </row>
     <row r="10" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="113" t="s">
         <v>287</v>
       </c>
-      <c r="B10" s="102"/>
-      <c r="C10" s="102"/>
-      <c r="D10" s="102"/>
+      <c r="B10" s="104"/>
+      <c r="C10" s="104"/>
+      <c r="D10" s="104"/>
     </row>
     <row r="11" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="113" t="s">
         <v>288</v>
       </c>
-      <c r="B11" s="102"/>
-      <c r="C11" s="102"/>
-      <c r="D11" s="102"/>
+      <c r="B11" s="104"/>
+      <c r="C11" s="104"/>
+      <c r="D11" s="104"/>
     </row>
     <row r="13" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="119" t="s">
+      <c r="A13" s="121" t="s">
         <v>289</v>
       </c>
-      <c r="B13" s="102"/>
-      <c r="C13" s="102"/>
-      <c r="D13" s="102"/>
+      <c r="B13" s="104"/>
+      <c r="C13" s="104"/>
+      <c r="D13" s="104"/>
     </row>
     <row r="14" spans="1:4" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="52" t="s">
@@ -10220,60 +10220,60 @@
       </c>
     </row>
     <row r="21" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="119" t="s">
+      <c r="A21" s="121" t="s">
         <v>313</v>
       </c>
-      <c r="B21" s="102"/>
-      <c r="C21" s="102"/>
-      <c r="D21" s="102"/>
+      <c r="B21" s="104"/>
+      <c r="C21" s="104"/>
+      <c r="D21" s="104"/>
     </row>
     <row r="22" spans="1:4" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="105" t="s">
+      <c r="A22" s="112" t="s">
         <v>314</v>
       </c>
-      <c r="B22" s="102"/>
-      <c r="C22" s="102"/>
-      <c r="D22" s="102"/>
+      <c r="B22" s="104"/>
+      <c r="C22" s="104"/>
+      <c r="D22" s="104"/>
     </row>
     <row r="23" spans="1:4" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="105" t="s">
+      <c r="A23" s="112" t="s">
         <v>315</v>
       </c>
-      <c r="B23" s="102"/>
-      <c r="C23" s="102"/>
-      <c r="D23" s="102"/>
+      <c r="B23" s="104"/>
+      <c r="C23" s="104"/>
+      <c r="D23" s="104"/>
     </row>
     <row r="24" spans="1:4" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="105" t="s">
+      <c r="A24" s="112" t="s">
         <v>316</v>
       </c>
-      <c r="B24" s="102"/>
-      <c r="C24" s="102"/>
-      <c r="D24" s="102"/>
+      <c r="B24" s="104"/>
+      <c r="C24" s="104"/>
+      <c r="D24" s="104"/>
     </row>
     <row r="25" spans="1:4" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="105" t="s">
+      <c r="A25" s="112" t="s">
         <v>317</v>
       </c>
-      <c r="B25" s="102"/>
-      <c r="C25" s="102"/>
-      <c r="D25" s="102"/>
+      <c r="B25" s="104"/>
+      <c r="C25" s="104"/>
+      <c r="D25" s="104"/>
     </row>
     <row r="26" spans="1:4" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="105" t="s">
+      <c r="A26" s="112" t="s">
         <v>318</v>
       </c>
-      <c r="B26" s="102"/>
-      <c r="C26" s="102"/>
-      <c r="D26" s="102"/>
+      <c r="B26" s="104"/>
+      <c r="C26" s="104"/>
+      <c r="D26" s="104"/>
     </row>
     <row r="27" spans="1:4" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="105" t="s">
+      <c r="A27" s="112" t="s">
         <v>319</v>
       </c>
-      <c r="B27" s="102"/>
-      <c r="C27" s="102"/>
-      <c r="D27" s="102"/>
+      <c r="B27" s="104"/>
+      <c r="C27" s="104"/>
+      <c r="D27" s="104"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -10380,22 +10380,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="120" t="s">
         <v>336</v>
       </c>
-      <c r="B1" s="102"/>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
+      <c r="B1" s="104"/>
+      <c r="C1" s="104"/>
+      <c r="D1" s="104"/>
+      <c r="E1" s="104"/>
     </row>
     <row r="2" spans="1:5" ht="34" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="113" t="s">
         <v>337</v>
       </c>
-      <c r="B2" s="102"/>
-      <c r="C2" s="102"/>
-      <c r="D2" s="102"/>
-      <c r="E2" s="102"/>
+      <c r="B2" s="104"/>
+      <c r="C2" s="104"/>
+      <c r="D2" s="104"/>
+      <c r="E2" s="104"/>
     </row>
     <row r="4" spans="1:5" ht="34" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="52" t="s">
@@ -10551,13 +10551,13 @@
       </c>
     </row>
     <row r="14" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="119" t="s">
+      <c r="A14" s="121" t="s">
         <v>380</v>
       </c>
-      <c r="B14" s="102"/>
-      <c r="C14" s="102"/>
-      <c r="D14" s="102"/>
-      <c r="E14" s="102"/>
+      <c r="B14" s="104"/>
+      <c r="C14" s="104"/>
+      <c r="D14" s="104"/>
+      <c r="E14" s="104"/>
     </row>
     <row r="15" spans="1:5" ht="34" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="52" t="s">
@@ -10713,49 +10713,49 @@
       </c>
     </row>
     <row r="25" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="120" t="s">
+      <c r="A25" s="122" t="s">
         <v>422</v>
       </c>
-      <c r="B25" s="102"/>
-      <c r="C25" s="102"/>
-      <c r="D25" s="102"/>
-      <c r="E25" s="102"/>
+      <c r="B25" s="104"/>
+      <c r="C25" s="104"/>
+      <c r="D25" s="104"/>
+      <c r="E25" s="104"/>
     </row>
     <row r="26" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="113" t="s">
         <v>423</v>
       </c>
-      <c r="B26" s="102"/>
-      <c r="C26" s="102"/>
-      <c r="D26" s="102"/>
-      <c r="E26" s="102"/>
+      <c r="B26" s="104"/>
+      <c r="C26" s="104"/>
+      <c r="D26" s="104"/>
+      <c r="E26" s="104"/>
     </row>
     <row r="27" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="113" t="s">
         <v>424</v>
       </c>
-      <c r="B27" s="102"/>
-      <c r="C27" s="102"/>
-      <c r="D27" s="102"/>
-      <c r="E27" s="102"/>
+      <c r="B27" s="104"/>
+      <c r="C27" s="104"/>
+      <c r="D27" s="104"/>
+      <c r="E27" s="104"/>
     </row>
     <row r="28" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="113" t="s">
         <v>425</v>
       </c>
-      <c r="B28" s="102"/>
-      <c r="C28" s="102"/>
-      <c r="D28" s="102"/>
-      <c r="E28" s="102"/>
+      <c r="B28" s="104"/>
+      <c r="C28" s="104"/>
+      <c r="D28" s="104"/>
+      <c r="E28" s="104"/>
     </row>
     <row r="29" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="113" t="s">
         <v>426</v>
       </c>
-      <c r="B29" s="102"/>
-      <c r="C29" s="102"/>
-      <c r="D29" s="102"/>
-      <c r="E29" s="102"/>
+      <c r="B29" s="104"/>
+      <c r="C29" s="104"/>
+      <c r="D29" s="104"/>
+      <c r="E29" s="104"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -17405,7 +17405,7 @@
       <c r="D58" s="31" t="s">
         <v>444</v>
       </c>
-      <c r="E58" s="122" t="s">
+      <c r="E58" s="102" t="s">
         <v>1337</v>
       </c>
       <c r="F58" s="32" t="s">
@@ -17455,7 +17455,7 @@
       <c r="D59" s="92" t="s">
         <v>447</v>
       </c>
-      <c r="E59" s="121" t="s">
+      <c r="E59" s="101" t="s">
         <v>1337</v>
       </c>
       <c r="F59" s="16" t="s">
@@ -17505,7 +17505,7 @@
       <c r="D60" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="E60" s="121" t="s">
+      <c r="E60" s="101" t="s">
         <v>1337</v>
       </c>
       <c r="F60" s="16" t="s">
@@ -17557,7 +17557,7 @@
       <c r="D61" s="92" t="s">
         <v>447</v>
       </c>
-      <c r="E61" s="121" t="s">
+      <c r="E61" s="101" t="s">
         <v>1337</v>
       </c>
       <c r="F61" s="16" t="s">

--- a/docs/migration-orders/davin-operational-manual/antigravity/migration-process-handbook-antigravity-v8.xlsx
+++ b/docs/migration-orders/davin-operational-manual/antigravity/migration-process-handbook-antigravity-v8.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SaaS Project\trading-alerts-saas-public\docs\migration-orders\davin-operational-manual\antigravity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82A82CD8-B323-4DB4-B19A-005D946CA127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0532CBDD-64D3-4DEB-A4D9-81EEB19049AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5417,7 +5417,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="123">
+  <cellXfs count="124">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -5695,7 +5695,11 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5710,16 +5714,15 @@
     <xf numFmtId="0" fontId="22" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9444,7 +9447,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="113" t="s">
         <v>194</v>
       </c>
       <c r="B1" s="104"/>
@@ -9453,7 +9456,7 @@
       <c r="E1" s="104"/>
     </row>
     <row r="2" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="113" t="s">
+      <c r="A2" s="114" t="s">
         <v>195</v>
       </c>
       <c r="B2" s="104"/>
@@ -9462,7 +9465,7 @@
       <c r="E2" s="104"/>
     </row>
     <row r="4" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="119" t="s">
+      <c r="A4" s="115" t="s">
         <v>196</v>
       </c>
       <c r="B4" s="104"/>
@@ -9471,7 +9474,7 @@
       <c r="E4" s="104"/>
     </row>
     <row r="5" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="113" t="s">
+      <c r="A5" s="114" t="s">
         <v>197</v>
       </c>
       <c r="B5" s="104"/>
@@ -9480,7 +9483,7 @@
       <c r="E5" s="104"/>
     </row>
     <row r="6" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="113" t="s">
+      <c r="A6" s="114" t="s">
         <v>198</v>
       </c>
       <c r="B6" s="104"/>
@@ -9489,7 +9492,7 @@
       <c r="E6" s="104"/>
     </row>
     <row r="7" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="113" t="s">
+      <c r="A7" s="114" t="s">
         <v>199</v>
       </c>
       <c r="B7" s="104"/>
@@ -9498,7 +9501,7 @@
       <c r="E7" s="104"/>
     </row>
     <row r="8" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="113" t="s">
+      <c r="A8" s="114" t="s">
         <v>200</v>
       </c>
       <c r="B8" s="104"/>
@@ -9507,7 +9510,7 @@
       <c r="E8" s="104"/>
     </row>
     <row r="10" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="115" t="s">
+      <c r="A10" s="117" t="s">
         <v>201</v>
       </c>
       <c r="B10" s="104"/>
@@ -9703,7 +9706,7 @@
       </c>
     </row>
     <row r="22" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="114"/>
+      <c r="A22" s="116"/>
       <c r="B22" s="106"/>
       <c r="C22" s="106"/>
       <c r="D22" s="106"/>
@@ -9761,7 +9764,7 @@
       </c>
     </row>
     <row r="28" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="116" t="s">
+      <c r="A28" s="118" t="s">
         <v>230</v>
       </c>
       <c r="B28" s="106"/>
@@ -9770,7 +9773,7 @@
       <c r="E28" s="107"/>
     </row>
     <row r="29" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="113" t="s">
+      <c r="A29" s="114" t="s">
         <v>231</v>
       </c>
       <c r="B29" s="104"/>
@@ -9896,7 +9899,7 @@
       <c r="A40" s="62" t="s">
         <v>252</v>
       </c>
-      <c r="B40" s="117" t="s">
+      <c r="B40" s="119" t="s">
         <v>253</v>
       </c>
       <c r="C40" s="106"/>
@@ -9983,14 +9986,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="B43:E43"/>
-    <mergeCell ref="A4:E4"/>
     <mergeCell ref="A47:E47"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A8:E8"/>
@@ -10004,6 +9999,14 @@
     <mergeCell ref="A31:E31"/>
     <mergeCell ref="B40:E40"/>
     <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="A4:E4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10032,7 +10035,7 @@
       <c r="D1" s="104"/>
     </row>
     <row r="2" spans="1:4" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="113" t="s">
+      <c r="A2" s="114" t="s">
         <v>268</v>
       </c>
       <c r="B2" s="104"/>
@@ -10104,7 +10107,7 @@
       <c r="D8" s="104"/>
     </row>
     <row r="9" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="113" t="s">
+      <c r="A9" s="114" t="s">
         <v>286</v>
       </c>
       <c r="B9" s="104"/>
@@ -10112,7 +10115,7 @@
       <c r="D9" s="104"/>
     </row>
     <row r="10" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="113" t="s">
+      <c r="A10" s="114" t="s">
         <v>287</v>
       </c>
       <c r="B10" s="104"/>
@@ -10120,7 +10123,7 @@
       <c r="D10" s="104"/>
     </row>
     <row r="11" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="113" t="s">
+      <c r="A11" s="114" t="s">
         <v>288</v>
       </c>
       <c r="B11" s="104"/>
@@ -10389,7 +10392,7 @@
       <c r="E1" s="104"/>
     </row>
     <row r="2" spans="1:5" ht="34" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="113" t="s">
+      <c r="A2" s="114" t="s">
         <v>337</v>
       </c>
       <c r="B2" s="104"/>
@@ -10722,7 +10725,7 @@
       <c r="E25" s="104"/>
     </row>
     <row r="26" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="113" t="s">
+      <c r="A26" s="114" t="s">
         <v>423</v>
       </c>
       <c r="B26" s="104"/>
@@ -10731,7 +10734,7 @@
       <c r="E26" s="104"/>
     </row>
     <row r="27" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="113" t="s">
+      <c r="A27" s="114" t="s">
         <v>424</v>
       </c>
       <c r="B27" s="104"/>
@@ -10740,7 +10743,7 @@
       <c r="E27" s="104"/>
     </row>
     <row r="28" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="113" t="s">
+      <c r="A28" s="114" t="s">
         <v>425</v>
       </c>
       <c r="B28" s="104"/>
@@ -10749,7 +10752,7 @@
       <c r="E28" s="104"/>
     </row>
     <row r="29" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="113" t="s">
+      <c r="A29" s="114" t="s">
         <v>426</v>
       </c>
       <c r="B29" s="104"/>
@@ -17594,157 +17597,157 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="62" spans="1:18" s="98" customFormat="1" ht="115.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62" s="93">
+    <row r="62" spans="1:18" s="33" customFormat="1" ht="115.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" s="29">
         <v>60</v>
       </c>
-      <c r="B62" s="94" t="s">
+      <c r="B62" s="34" t="s">
         <v>886</v>
       </c>
-      <c r="C62" s="95" t="s">
+      <c r="C62" s="35" t="s">
         <v>636</v>
       </c>
-      <c r="D62" s="96" t="s">
+      <c r="D62" s="31" t="s">
         <v>444</v>
       </c>
-      <c r="E62" s="97" t="s">
+      <c r="E62" s="32" t="s">
         <v>1356</v>
       </c>
-      <c r="F62" s="97" t="s">
+      <c r="F62" s="32" t="s">
         <v>1357</v>
       </c>
-      <c r="G62" s="97" t="s">
+      <c r="G62" s="32" t="s">
         <v>1358</v>
       </c>
-      <c r="H62" s="97" t="s">
+      <c r="H62" s="32" t="s">
         <v>1069</v>
       </c>
-      <c r="I62" s="97" t="s">
-        <v>1061</v>
-      </c>
-      <c r="J62" s="97" t="s">
+      <c r="I62" s="32" t="s">
+        <v>1061</v>
+      </c>
+      <c r="J62" s="32" t="s">
         <v>1070</v>
       </c>
-      <c r="K62" s="97" t="s">
+      <c r="K62" s="32" t="s">
         <v>1359</v>
       </c>
-      <c r="L62" s="97" t="s">
+      <c r="L62" s="32" t="s">
         <v>1360</v>
       </c>
-      <c r="M62" s="97" t="s">
+      <c r="M62" s="32" t="s">
         <v>1064</v>
       </c>
-      <c r="N62" s="97" t="s">
+      <c r="N62" s="32" t="s">
         <v>1065</v>
       </c>
-      <c r="O62" s="97" t="s">
-        <v>1061</v>
-      </c>
-      <c r="P62" s="97" t="s">
-        <v>1061</v>
-      </c>
-      <c r="Q62" s="97" t="s">
+      <c r="O62" s="32" t="s">
+        <v>1061</v>
+      </c>
+      <c r="P62" s="32" t="s">
+        <v>1061</v>
+      </c>
+      <c r="Q62" s="32" t="s">
         <v>1161</v>
       </c>
-      <c r="R62" s="97" t="s">
+      <c r="R62" s="32" t="s">
         <v>1361</v>
       </c>
     </row>
-    <row r="63" spans="1:18" ht="158.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A63" s="2">
+    <row r="63" spans="1:18" s="33" customFormat="1" ht="158.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63" s="29">
         <v>61</v>
       </c>
-      <c r="B63" s="14" t="s">
+      <c r="B63" s="34" t="s">
         <v>892</v>
       </c>
-      <c r="C63" s="15" t="s">
+      <c r="C63" s="35" t="s">
         <v>636</v>
       </c>
-      <c r="D63" s="92" t="s">
+      <c r="D63" s="31" t="s">
         <v>447</v>
       </c>
-      <c r="E63" s="13"/>
-      <c r="F63" s="16" t="s">
+      <c r="E63" s="30"/>
+      <c r="F63" s="32" t="s">
         <v>1362</v>
       </c>
-      <c r="G63" s="16" t="s">
+      <c r="G63" s="32" t="s">
         <v>1104</v>
       </c>
-      <c r="H63" s="16"/>
-      <c r="I63" s="16" t="s">
+      <c r="H63" s="32"/>
+      <c r="I63" s="32" t="s">
         <v>1363</v>
       </c>
-      <c r="J63" s="16" t="s">
-        <v>1061</v>
-      </c>
-      <c r="K63" s="16" t="s">
+      <c r="J63" s="32" t="s">
+        <v>1061</v>
+      </c>
+      <c r="K63" s="32" t="s">
         <v>1364</v>
       </c>
-      <c r="L63" s="3"/>
-      <c r="M63" s="3"/>
-      <c r="N63" s="16" t="s">
+      <c r="L63" s="31"/>
+      <c r="M63" s="31"/>
+      <c r="N63" s="32" t="s">
         <v>1065</v>
       </c>
-      <c r="O63" s="16" t="s">
-        <v>1061</v>
-      </c>
-      <c r="P63" s="16" t="s">
+      <c r="O63" s="32" t="s">
+        <v>1061</v>
+      </c>
+      <c r="P63" s="32" t="s">
         <v>1365</v>
       </c>
-      <c r="Q63" s="16" t="s">
+      <c r="Q63" s="32" t="s">
         <v>1366</v>
       </c>
-      <c r="R63" s="16" t="s">
-        <v>1061</v>
-      </c>
-    </row>
-    <row r="64" spans="1:18" ht="86.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A64" s="2">
+      <c r="R63" s="32" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" s="98" customFormat="1" ht="86.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A64" s="93">
         <v>62</v>
       </c>
-      <c r="B64" s="14" t="s">
+      <c r="B64" s="94" t="s">
         <v>898</v>
       </c>
-      <c r="C64" s="15" t="s">
+      <c r="C64" s="95" t="s">
         <v>636</v>
       </c>
-      <c r="D64" s="3" t="s">
+      <c r="D64" s="96" t="s">
         <v>438</v>
       </c>
-      <c r="E64" s="13"/>
-      <c r="F64" s="16" t="s">
+      <c r="E64" s="123"/>
+      <c r="F64" s="97" t="s">
         <v>1367</v>
       </c>
-      <c r="G64" s="16" t="s">
+      <c r="G64" s="97" t="s">
         <v>1368</v>
       </c>
-      <c r="H64" s="16" t="s">
+      <c r="H64" s="97" t="s">
         <v>1069</v>
       </c>
-      <c r="I64" s="16" t="s">
-        <v>1061</v>
-      </c>
-      <c r="J64" s="16" t="s">
+      <c r="I64" s="97" t="s">
+        <v>1061</v>
+      </c>
+      <c r="J64" s="97" t="s">
         <v>1070</v>
       </c>
-      <c r="K64" s="16" t="s">
+      <c r="K64" s="97" t="s">
         <v>1369</v>
       </c>
-      <c r="L64" s="3"/>
-      <c r="M64" s="3"/>
-      <c r="N64" s="16" t="s">
+      <c r="L64" s="96"/>
+      <c r="M64" s="96"/>
+      <c r="N64" s="97" t="s">
         <v>1065</v>
       </c>
-      <c r="O64" s="16" t="s">
-        <v>1061</v>
-      </c>
-      <c r="P64" s="16" t="s">
-        <v>1061</v>
-      </c>
-      <c r="Q64" s="16" t="s">
+      <c r="O64" s="97" t="s">
+        <v>1061</v>
+      </c>
+      <c r="P64" s="97" t="s">
+        <v>1061</v>
+      </c>
+      <c r="Q64" s="97" t="s">
         <v>1370</v>
       </c>
-      <c r="R64" s="16" t="s">
+      <c r="R64" s="97" t="s">
         <v>1061</v>
       </c>
     </row>
@@ -17940,51 +17943,51 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="69" spans="1:18" s="33" customFormat="1" ht="158.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A69" s="2">
+    <row r="69" spans="1:18" s="98" customFormat="1" ht="158.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A69" s="93">
         <v>67</v>
       </c>
-      <c r="B69" s="14" t="s">
+      <c r="B69" s="94" t="s">
         <v>927</v>
       </c>
-      <c r="C69" s="15" t="s">
+      <c r="C69" s="95" t="s">
         <v>636</v>
       </c>
-      <c r="D69" s="92" t="s">
+      <c r="D69" s="96" t="s">
         <v>447</v>
       </c>
-      <c r="E69" s="13"/>
-      <c r="F69" s="16" t="s">
+      <c r="E69" s="123"/>
+      <c r="F69" s="97" t="s">
         <v>1383</v>
       </c>
-      <c r="G69" s="16" t="s">
+      <c r="G69" s="97" t="s">
         <v>1104</v>
       </c>
-      <c r="H69" s="16"/>
-      <c r="I69" s="16" t="s">
+      <c r="H69" s="97"/>
+      <c r="I69" s="97" t="s">
         <v>1384</v>
       </c>
-      <c r="J69" s="16" t="s">
-        <v>1061</v>
-      </c>
-      <c r="K69" s="16" t="s">
+      <c r="J69" s="97" t="s">
+        <v>1061</v>
+      </c>
+      <c r="K69" s="97" t="s">
         <v>1385</v>
       </c>
-      <c r="L69" s="3"/>
-      <c r="M69" s="3"/>
-      <c r="N69" s="16" t="s">
+      <c r="L69" s="96"/>
+      <c r="M69" s="96"/>
+      <c r="N69" s="97" t="s">
         <v>1065</v>
       </c>
-      <c r="O69" s="16" t="s">
-        <v>1061</v>
-      </c>
-      <c r="P69" s="16" t="s">
-        <v>1061</v>
-      </c>
-      <c r="Q69" s="16" t="s">
+      <c r="O69" s="97" t="s">
+        <v>1061</v>
+      </c>
+      <c r="P69" s="97" t="s">
+        <v>1061</v>
+      </c>
+      <c r="Q69" s="97" t="s">
         <v>1386</v>
       </c>
-      <c r="R69" s="16" t="s">
+      <c r="R69" s="97" t="s">
         <v>1387</v>
       </c>
     </row>
